--- a/randomizer/MoveData.xlsx
+++ b/randomizer/MoveData.xlsx
@@ -17411,7 +17411,7 @@
         <v>650</v>
       </c>
       <c r="B625" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C625" s="1" t="s">
         <v>14</v>
